--- a/onagawa_water_tariff/06_capital_plan_update/09_assumption_switch_cost_calc.xlsx
+++ b/onagawa_water_tariff/06_capital_plan_update/09_assumption_switch_cost_calc.xlsx
@@ -249,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -320,6 +320,10 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="18" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8781,7 +8785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -8809,6 +8813,20 @@
           <t>「01_設定」で選択できる組み合わせのうち、代表的なものを並べたものです。金額は千円。</t>
         </is>
       </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="48" t="inlineStr">
+        <is>
+          <t>【この版は中間報告書（改訂版）の前提と一致しません】　計算根拠には使用しないでください。　本文の数値は 09_interim_report/onagawa_adopted_calc.xlsx（採用計算表）で再現します。</t>
+        </is>
+      </c>
+      <c r="B3" s="49" t="n"/>
+      <c r="C3" s="49" t="n"/>
+      <c r="D3" s="49" t="n"/>
+      <c r="E3" s="49" t="n"/>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="49" t="n"/>
+      <c r="H3" s="49" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr"/>
